--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>fr-lm-observation-assessment.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3093,13 +3097,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3167,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3196,10 +3200,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3250,7 +3254,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3267,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3296,10 +3300,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3350,7 +3354,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3367,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3393,13 +3397,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3450,7 +3454,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3467,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3493,13 +3497,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3550,7 +3554,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
